--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2405-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2405-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0347B5F7-7421-4444-BF64-02E97D88EDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52821829-B843-4DFB-AB78-5D06509BF34E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{89BC0887-C349-44BB-80FA-8F16D53111E1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2374F2C1-6AC5-45D4-AA24-15225CA4C511}"/>
   </bookViews>
   <sheets>
     <sheet name="2405-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1481,28 +1481,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F589890-5C33-455D-88EC-1DF7AFC281AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C78F44A5-B7AB-45F2-909E-B44CCBF1165F}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1572,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1692,7 +1692,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2024</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2023</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2022</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2021</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2020</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2019</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
         <v>29</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>29</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2018</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2017</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2016</v>
       </c>
@@ -3596,7 +3596,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>2015</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2014</v>
       </c>
@@ -3740,7 +3740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>2013</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2012</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <v>2011</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2010</v>
       </c>
@@ -4028,7 +4028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <v>2009</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>2008</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <v>2007</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>2006</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
         <v>2005</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>2004</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>4.95</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="36">
         <v>2003</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>19.2</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>2002</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>8.0299999999999994</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="36">
         <v>2001</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>2000</v>
       </c>
@@ -4748,7 +4748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="36">
         <v>1999</v>
       </c>
@@ -4820,7 +4820,7 @@
         <v>33.299999999999997</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38">
         <v>1998</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>8.6999999999999993</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="36">
         <v>1997</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="38">
         <v>1996</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="36">
         <v>1995</v>
       </c>
@@ -5108,7 +5108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="38">
         <v>1994</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="36">
         <v>1993</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="s">
         <v>47</v>
       </c>
